--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,69 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>QuestionnaireCreator_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tools QuestionnaireCreator</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' end-to-end: content saved via the dialog actually lands in the target project</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790763561365'), fills the required 'Title' field ('ToolsQA_A2PItem_1790763561365'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Target project: ToolsQA_A2P_1790763561365; Item title: ToolsQA_A2PItem_1790763561365; Question: Is [entity] carrying on a business?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790763561365'
+2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790763561365', fill Title 'ToolsQA_A2PItem_1790763561365', click Add
+4. Verify the AddToProject network call succeeded
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790763561365', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1790763561365'; reset the editor via Start Over</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790763561365'), fills the required 'Title' field ('ToolsQA_A2PItem_1790763561365'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790763561365' into 'ToolsQA_A2P_1790763561365', confirmed by cross-page verification on the Projects page's item table.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] AddToProject API call returned isSuccess=true
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790763561365'</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790763561365'), fills the required 'Title' field ('ToolsQA_A2PItem_1790763561365'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790766741049'), fills the required 'Title' field ('ToolsQA_A2PItem_1790766741049'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -897,33 +897,33 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Target project: ToolsQA_A2P_1790763561365; Item title: ToolsQA_A2PItem_1790763561365; Question: Is [entity] carrying on a business?</t>
+          <t>Target project: ToolsQA_A2P_1790766741049; Item title: ToolsQA_A2PItem_1790766741049; Question: Is [entity] carrying on a business?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790763561365'
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790766741049'
 2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790763561365', fill Title 'ToolsQA_A2PItem_1790763561365', click Add
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790766741049', fill Title 'ToolsQA_A2PItem_1790766741049', click Add
 4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790763561365', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1790763561365'; reset the editor via Start Over</t>
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790766741049', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1790766741049'; reset the editor via Start Over</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790763561365'), fills the required 'Title' field ('ToolsQA_A2PItem_1790763561365'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790766741049'), fills the required 'Title' field ('ToolsQA_A2PItem_1790766741049'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790763561365' into 'ToolsQA_A2P_1790763561365', confirmed by cross-page verification on the Projects page's item table.</t>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790766741049' into 'ToolsQA_A2P_1790766741049', confirmed by cross-page verification on the Projects page's item table.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790763561365'</t>
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790766741049'</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790766741049'), fills the required 'Title' field ('ToolsQA_A2PItem_1790766741049'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790770741326'), fills the required 'Title' field ('ToolsQA_A2PItem_1790770741326'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -897,33 +897,33 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Target project: ToolsQA_A2P_1790766741049; Item title: ToolsQA_A2PItem_1790766741049; Question: Is [entity] carrying on a business?</t>
+          <t>Target project: ToolsQA_A2P_1790770741326; Item title: ToolsQA_A2PItem_1790770741326; Question: Is [entity] carrying on a business?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790766741049'
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790770741326'
 2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790766741049', fill Title 'ToolsQA_A2PItem_1790766741049', click Add
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790770741326', fill Title 'ToolsQA_A2PItem_1790770741326', click Add
 4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790766741049', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1790766741049'; reset the editor via Start Over</t>
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790770741326', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1790770741326'; reset the editor via Start Over</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790766741049'), fills the required 'Title' field ('ToolsQA_A2PItem_1790766741049'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790770741326'), fills the required 'Title' field ('ToolsQA_A2PItem_1790770741326'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790766741049' into 'ToolsQA_A2P_1790766741049', confirmed by cross-page verification on the Projects page's item table.</t>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790770741326' into 'ToolsQA_A2P_1790770741326', confirmed by cross-page verification on the Projects page's item table.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790766741049'</t>
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790770741326'</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790770741326'), fills the required 'Title' field ('ToolsQA_A2PItem_1790770741326'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790772108510'), fills the required 'Title' field ('ToolsQA_A2PItem_1790772108510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -897,33 +897,33 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Target project: ToolsQA_A2P_1790770741326; Item title: ToolsQA_A2PItem_1790770741326; Question: Is [entity] carrying on a business?</t>
+          <t>Target project: ToolsQA_A2P_1790772108510; Item title: ToolsQA_A2PItem_1790772108510; Question: Is [entity] carrying on a business?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790770741326'
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790772108510'
 2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790770741326', fill Title 'ToolsQA_A2PItem_1790770741326', click Add
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790772108510', fill Title 'ToolsQA_A2PItem_1790772108510', click Add
 4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790770741326', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1790770741326'; reset the editor via Start Over</t>
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790772108510', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1790772108510'; reset the editor via Start Over</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790770741326'), fills the required 'Title' field ('ToolsQA_A2PItem_1790770741326'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790772108510'), fills the required 'Title' field ('ToolsQA_A2PItem_1790772108510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790770741326' into 'ToolsQA_A2P_1790770741326', confirmed by cross-page verification on the Projects page's item table.</t>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790772108510' into 'ToolsQA_A2P_1790772108510', confirmed by cross-page verification on the Projects page's item table.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790770741326'</t>
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790772108510'</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790772108510'), fills the required 'Title' field ('ToolsQA_A2PItem_1790772108510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791196073510'), fills the required 'Title' field ('ToolsQA_A2PItem_1791196073510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -897,33 +897,33 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Target project: ToolsQA_A2P_1790772108510; Item title: ToolsQA_A2PItem_1790772108510; Question: Is [entity] carrying on a business?</t>
+          <t>Target project: ToolsQA_A2P_1791196073510; Item title: ToolsQA_A2PItem_1791196073510; Question: Is [entity] carrying on a business?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1790772108510'
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1791196073510'
 2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1790772108510', fill Title 'ToolsQA_A2PItem_1790772108510', click Add
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1791196073510', fill Title 'ToolsQA_A2PItem_1791196073510', click Add
 4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1790772108510', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1790772108510'; reset the editor via Start Over</t>
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1791196073510', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1791196073510'; reset the editor via Start Over</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1790772108510'), fills the required 'Title' field ('ToolsQA_A2PItem_1790772108510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791196073510'), fills the required 'Title' field ('ToolsQA_A2PItem_1791196073510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1790772108510' into 'ToolsQA_A2P_1790772108510', confirmed by cross-page verification on the Projects page's item table.</t>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1791196073510' into 'ToolsQA_A2P_1791196073510', confirmed by cross-page verification on the Projects page's item table.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1790772108510'</t>
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1791196073510'</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791196073510'), fills the required 'Title' field ('ToolsQA_A2PItem_1791196073510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791287869542'), fills the required 'Title' field ('ToolsQA_A2PItem_1791287869542'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -897,33 +897,33 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Target project: ToolsQA_A2P_1791196073510; Item title: ToolsQA_A2PItem_1791196073510; Question: Is [entity] carrying on a business?</t>
+          <t>Target project: ToolsQA_A2P_1791287869542; Item title: ToolsQA_A2PItem_1791287869542; Question: Is [entity] carrying on a business?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1791196073510'
+          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1791287869542'
 2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1791196073510', fill Title 'ToolsQA_A2PItem_1791196073510', click Add
+3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1791287869542', fill Title 'ToolsQA_A2PItem_1791287869542', click Add
 4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1791196073510', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1791196073510'; reset the editor via Start Over</t>
+5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1791287869542', verify the item row's Title matches
+6. Clean up: delete 'ToolsQA_A2P_1791287869542'; reset the editor via Start Over</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791196073510'), fills the required 'Title' field ('ToolsQA_A2PItem_1791196073510'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
+          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791287869542'), fills the required 'Title' field ('ToolsQA_A2PItem_1791287869542'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1791196073510' into 'ToolsQA_A2P_1791196073510', confirmed by cross-page verification on the Projects page's item table.</t>
+          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1791287869542' into 'ToolsQA_A2P_1791287869542', confirmed by cross-page verification on the Projects page's item table.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1791196073510'</t>
+[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1791287869542'</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -44,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -554,17 +554,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Questionnaire Creator loaded correctly at https://regplus.kaz.com.bd/wta/QuestionnaireCreator, and 'Add to Project' appeared once content was inserted.</t>
+          <t>Questionnaire Creator did not load as expected (url_ok=True, heading_ok=True, start_over_ok=True, editor_ok=True, add_ok=False).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Questionnaire Creator loads with all key controls present</t>
+          <t>[FAIL] Questionnaire Creator loads with all key controls present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -615,320 +615,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Is [entity] carrying on a business?' correctly inserted content into the editor (4 -&gt; 318 chars).</t>
+          <t>The editor's content did not grow as expected (4 -&gt; 4 chars).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Editor content grew after clicking the question</t>
+          <t>[FAIL] Editor content grew after clicking the question</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>QuestionnaireCreator_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tools QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>'Start Over' shows a confirmation dialog before clearing</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start Over' must show a 'Confirm Start Over' dialog with 'No' and 'Yes' options, rather than clearing the editor immediately.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Questionnaire Creator, with at least one question already inserted ('Start Over' is disabled - by design - when there's nothing to reset, so this test ensures that precondition itself rather than assuming it).</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Question: Is [entity] carrying on a business?</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Questionnaire Creator
-2. Ensure the editor has content (insert 'Is [entity] carrying on a business?' if empty)
-3. Click 'Start Over'
-4. Verify the confirmation dialog and its No/Yes buttons are visible</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start Over' must show a 'Confirm Start Over' dialog with 'No' and 'Yes' options, rather than clearing the editor immediately.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>'Start Over' correctly showed a confirmation dialog with No/Yes before clearing anything.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Confirm Start Over' dialog with No/Yes is shown</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>QuestionnaireCreator_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Tools QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'No' on the Start Over confirmation keeps the editor content</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'No' must leave the editor's content unchanged (the reset must not happen until 'Yes' is confirmed).</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Questionnaire Creator.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Question: Is [entity] carrying on a business?</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Questionnaire Creator
-2. Click 'Is [entity] carrying on a business?' to add content
-3. Click 'Start Over', then 'No'
-4. Verify the editor content is unchanged</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'No' must leave the editor's content unchanged (the reset must not happen until 'Yes' is confirmed).</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Declining Start Over correctly left the editor content unchanged (318 chars).</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Editor content is unchanged after declining Start Over</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>QuestionnaireCreator_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Tools QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start Over' clears the editor</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'Yes' must empty the editor's content.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Questionnaire Creator.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Question: Is [entity] carrying on a business?</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Questionnaire Creator
-2. Click 'Is [entity] carrying on a business?' to add content
-3. Click 'Start Over', then 'Yes'
-4. Verify the editor is empty</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'Yes' must empty the editor's content.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start Over' correctly cleared the editor.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Editor is empty after confirming Start Over</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>QuestionnaireCreator_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Tools QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' opens a project-target dialog</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' only renders once the editor has content (confirmed live - see pages/tools_questionnaire_creator_page.py), so this case inserts a question first. Clicking 'Add to Project' must then open a dialog for saving the current questionnaire content into a Tools &gt; Projects project.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Questionnaire Creator.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Question: Is [entity] carrying on a business?</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Questionnaire Creator
-2. Click 'Is [entity] carrying on a business?' to add content
-3. Click 'Add to Project'
-4. Verify a dialog/modal opens</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' only renders once the editor has content (confirmed live - see pages/tools_questionnaire_creator_page.py), so this case inserts a question first. Clicking 'Add to Project' must then open a dialog for saving the current questionnaire content into a Tools &gt; Projects project.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' correctly opened a dialog (5 -&gt; 6).</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] A dialog opened after clicking 'Add to Project'</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>QuestionnaireCreator_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Tools QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' end-to-end: content saved via the dialog actually lands in the target project</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791287869542'), fills the required 'Title' field ('ToolsQA_A2PItem_1791287869542'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Target project: ToolsQA_A2P_1791287869542; Item title: ToolsQA_A2PItem_1791287869542; Question: Is [entity] carrying on a business?</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Tools &gt; Projects; create 'ToolsQA_A2P_1791287869542'
-2. Open Questionnaire Creator and insert 'Is [entity] carrying on a business?'
-3. Click 'Add to Project', switch to 'To an Existing Project', select 'ToolsQA_A2P_1791287869542', fill Title 'ToolsQA_A2PItem_1791287869542', click Add
-4. Verify the AddToProject network call succeeded
-5. Open Tools &gt; Projects, select 'ToolsQA_A2P_1791287869542', verify the item row's Title matches
-6. Clean up: delete 'ToolsQA_A2P_1791287869542'; reset the editor via Start Over</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Closes the gap deliberately left open by QuestionnaireCreator_06 (which only checked the dialog opens): inserts 'Is [entity] carrying on a business?', opens 'Add to Project', switches to 'To an Existing Project' (a target project created via Tools &gt; Projects for this test, 'ToolsQA_A2P_1791287869542'), fills the required 'Title' field ('ToolsQA_A2PItem_1791287869542'), submits, and then cross-page-verifies on the Projects page that this exact item row was really saved - proving the complete business functionality, not just that a modal opens. Confirmed live via network capture: submitting fires 'POST .../api/Project/AddToProject' with the Row/ProjectName/ProjectId payload -&gt; 200 '{"isSuccess":true}' (see pages/tools_questionnaire_creator_page.py).</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' correctly saved 'ToolsQA_A2PItem_1791287869542' into 'ToolsQA_A2P_1791287869542', confirmed by cross-page verification on the Projects page's item table.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] AddToProject API call returned isSuccess=true
-[PASS] The saved item's Title cell matches 'ToolsQA_A2PItem_1791287869542'</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
+++ b/test_data/Tools QuestionnaireCreator/Tools QuestionnaireCreator_Test_Cases.xlsx
@@ -44,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -554,17 +554,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Questionnaire Creator did not load as expected (url_ok=True, heading_ok=True, start_over_ok=True, editor_ok=True, add_ok=False).</t>
+          <t>Questionnaire Creator loaded correctly at https://regplus.reganalytics.com/wta/QuestionnaireCreator, and 'Add to Project' appeared once content was inserted.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Questionnaire Creator loads with all key controls present</t>
+          <t>[PASS] Questionnaire Creator loads with all key controls present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -615,17 +615,77 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The editor's content did not grow as expected (4 -&gt; 4 chars).</t>
+          <t>Clicking 'Is [entity] carrying on a business?' correctly inserted content into the editor (4 -&gt; 318 chars).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Editor content grew after clicking the question</t>
+          <t>[PASS] Editor content grew after clicking the question</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>QuestionnaireCreator_05</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tools QuestionnaireCreator</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Confirming 'Start Over' clears the editor</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'Yes' must empty the editor's content.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Questionnaire Creator.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Question: Is [entity] carrying on a business?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Questionnaire Creator
+2. Click 'Is [entity] carrying on a business?' to add content
+3. Click 'Start Over', then 'Yes'
+4. Verify the editor is empty</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>After inserting 'Is [entity] carrying on a business?', clicking 'Start Over' then 'Yes' must empty the editor's content.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Confirming 'Start Over' correctly cleared the editor.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Editor is empty after confirming Start Over</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
